--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486334_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486334_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1993</v>
+        <v>3.6097</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7376</v>
+        <v>2.1788</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4617</v>
+        <v>1.4309</v>
       </c>
       <c r="G2" t="n">
         <v>0.3582</v>
@@ -610,13 +610,13 @@
         <v>1.5225</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8241</v>
+        <v>1.2344</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1152</v>
+        <v>0.5564</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7089</v>
+        <v>0.678</v>
       </c>
       <c r="V2" t="n">
         <v>1.582</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7355</v>
+        <v>2.6614</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6139</v>
+        <v>1.5706</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1216</v>
+        <v>1.0908</v>
       </c>
       <c r="G3" t="n">
         <v>1.278</v>
@@ -688,13 +688,13 @@
         <v>0.435</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1355</v>
+        <v>1.0614</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4266</v>
+        <v>0.3833</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7089</v>
+        <v>0.678</v>
       </c>
       <c r="V3" t="n">
         <v>-0.113</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1863</v>
+        <v>0.4369</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.2273</v>
+        <v>-1.6685</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4136</v>
+        <v>2.1054</v>
       </c>
       <c r="G4" t="n">
         <v>-0.5448</v>
@@ -766,13 +766,13 @@
         <v>1.0875</v>
       </c>
       <c r="S4" t="n">
-        <v>0.536</v>
+        <v>0.7865</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1815</v>
+        <v>0.3773</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7174</v>
+        <v>0.4092</v>
       </c>
       <c r="V4" t="n">
         <v>0.1952</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. NWAOKORIE</t>
+          <t>D. DUSCAK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0459</v>
+        <v>-0.7849</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.006</v>
+        <v>0.2131</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.04</v>
+        <v>-0.998</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.6494</v>
+        <v>-0.0282</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.36</v>
+        <v>-1.1557</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.2894</v>
+        <v>1.1275</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.1861</v>
+        <v>1.3896</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.2132</v>
+        <v>0.2222</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.9729</v>
+        <v>1.1674</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.4633</v>
+        <v>-1.4178</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1468</v>
+        <v>-1.3779</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.3164</v>
+        <v>-0.0399</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>3.6311</v>
+        <v>0.012</v>
       </c>
       <c r="T5" t="n">
-        <v>2.8348</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7962</v>
+        <v>0.1009</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4074</v>
+        <v>-0.9862</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5204</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.113</v>
+        <v>-0.9862</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0674</v>
+        <v>-1.025</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9873</v>
+        <v>-1.0991</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.08</v>
+        <v>0.0741</v>
       </c>
       <c r="G6" t="n">
         <v>0.4909</v>
@@ -922,13 +922,13 @@
         <v>1.0875</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2073</v>
+        <v>0.2497</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3581</v>
+        <v>0.2464</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1508</v>
+        <v>0.0033</v>
       </c>
       <c r="V6" t="n">
         <v>-0.678</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. DUSCAK</t>
+          <t>G. PARHAM II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4237</v>
+        <v>-1.2981</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3024</v>
+        <v>-0.1636</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1213</v>
+        <v>-1.1345</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0282</v>
+        <v>-1.4176</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1557</v>
+        <v>-0.4351</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1275</v>
+        <v>-0.9825</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3896</v>
+        <v>0.9636</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2222</v>
+        <v>1.0767</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1674</v>
+        <v>-0.1131</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4178</v>
+        <v>-2.3812</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3779</v>
+        <v>-1.5118</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0399</v>
+        <v>-0.8694</v>
       </c>
       <c r="P7" t="n">
         <v>0.2175</v>
@@ -1000,22 +1000,22 @@
         <v>1.305</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6268</v>
+        <v>0.015</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6044</v>
+        <v>-0.0396</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0224</v>
+        <v>0.0547</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9862</v>
+        <v>-0.113</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9862</v>
+        <v>-0.113</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5812</v>
+        <v>-1.5389</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9198</v>
+        <v>-1.0316</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6614</v>
+        <v>-0.5073</v>
       </c>
       <c r="G8" t="n">
         <v>0.3004</v>
@@ -1078,13 +1078,13 @@
         <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3189</v>
+        <v>1.3612</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6357</v>
+        <v>0.524</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6832</v>
+        <v>0.8373</v>
       </c>
       <c r="V8" t="n">
         <v>-1.243</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. PARHAM II</t>
+          <t>F. NWAOKORIE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3339</v>
+        <v>-1.8889</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0144</v>
+        <v>-1.7256</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3194</v>
+        <v>-0.1633</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4176</v>
+        <v>-4.6494</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4351</v>
+        <v>-2.36</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9825</v>
+        <v>-2.2894</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9636</v>
+        <v>-2.1861</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0767</v>
+        <v>-1.2132</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1131</v>
+        <v>-0.9729</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3812</v>
+        <v>-2.4633</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.5118</v>
+        <v>-1.1468</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8694</v>
+        <v>-1.3164</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2175</v>
+        <v>-0.435</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R9" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0207</v>
+        <v>1.7881</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8904</v>
+        <v>1.1152</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1303</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.113</v>
+        <v>1.4074</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.5204</v>
       </c>
       <c r="X9" t="n">
         <v>-0.113</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. COSIALLS BORRAS</t>
+          <t>R. LOBACO MUÑOZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4344</v>
+        <v>-2.9044</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9528</v>
+        <v>-2.3078</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.4816</v>
+        <v>-0.5965</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5303</v>
+        <v>-4.9551</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.3478</v>
+        <v>-1.025</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8176</v>
+        <v>-3.9301</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1994</v>
+        <v>-1.3084</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.8879</v>
+        <v>0.3713</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6885</v>
+        <v>-1.6797</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3309</v>
+        <v>-3.6467</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4599</v>
+        <v>-1.3963</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1291</v>
+        <v>-2.2504</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.0875</v>
+        <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.1751</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1388</v>
+        <v>1.1467</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3341</v>
+        <v>0.0457</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1953</v>
+        <v>1.101</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9554</v>
+        <v>0.904</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.9554</v>
+        <v>-0.226</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. LOBACO MUÑOZ</t>
+          <t>R. COSIALLS BORRAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7445</v>
+        <v>-3.3236</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4254</v>
+        <v>-0.9961</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3191</v>
+        <v>-2.3275</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.9551</v>
+        <v>-1.5303</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.025</v>
+        <v>-2.3478</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.9301</v>
+        <v>0.8176</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3084</v>
+        <v>-0.1994</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3713</v>
+        <v>-0.8879</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.6797</v>
+        <v>0.6885</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.6467</v>
+        <v>-1.3309</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3963</v>
+        <v>-1.4599</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.2504</v>
+        <v>0.1291</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1751</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3066</v>
+        <v>0.2497</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0719</v>
+        <v>0.2908</v>
       </c>
       <c r="U11" t="n">
-        <v>1.3785</v>
+        <v>-0.0412</v>
       </c>
       <c r="V11" t="n">
-        <v>0.904</v>
+        <v>-0.9554</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.226</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.5099</v>
+        <v>-6.055799999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.483899999999999</v>
+        <v>-5.0298</v>
       </c>
       <c r="F12" t="n">
         <v>-1.0259</v>
@@ -1369,7 +1369,7 @@
         <v>3.0134</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7687999999999996</v>
+        <v>-0.7687999999999998</v>
       </c>
       <c r="M12" t="n">
         <v>-12.9426</v>
@@ -1390,16 +1390,16 @@
         <v>11.9627</v>
       </c>
       <c r="S12" t="n">
-        <v>7.450799999999999</v>
+        <v>7.9047</v>
       </c>
       <c r="T12" t="n">
-        <v>2.9563</v>
+        <v>3.4106</v>
       </c>
       <c r="U12" t="n">
-        <v>4.4943</v>
+        <v>4.4941</v>
       </c>
       <c r="V12" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>4.5406</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.7603</v>
+        <v>6.5657</v>
       </c>
       <c r="E13" t="n">
-        <v>3.6876</v>
+        <v>3.7993</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0727</v>
+        <v>2.7663</v>
       </c>
       <c r="G13" t="n">
         <v>5.5471</v>
@@ -1468,13 +1468,13 @@
         <v>2.3926</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.2642</v>
+        <v>-1.4589</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0959</v>
+        <v>-0.9842</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1683</v>
+        <v>-0.4747</v>
       </c>
       <c r="V13" t="n">
         <v>2.2599</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7964</v>
+        <v>4.5055</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4365</v>
+        <v>3.8835</v>
       </c>
       <c r="F14" t="n">
-        <v>0.36</v>
+        <v>0.6221</v>
       </c>
       <c r="G14" t="n">
         <v>5.5861</v>
@@ -1546,13 +1546,13 @@
         <v>2.1751</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4199</v>
+        <v>-0.7108</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0274</v>
+        <v>-0.5804</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3925</v>
+        <v>-0.1304</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3698</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. SOLA IDDRISU</t>
+          <t>V. ARTEAGA GONZALEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0666</v>
+        <v>0.9728</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8774999999999999</v>
+        <v>-0.1576</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1891</v>
+        <v>1.1304</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4968</v>
+        <v>1.7343</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0944</v>
+        <v>1.0737</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4024</v>
+        <v>0.6606</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2404</v>
+        <v>1.0251</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9855</v>
+        <v>1.0251</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.7451</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7372</v>
+        <v>0.7091</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0799</v>
+        <v>0.0486</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3426</v>
+        <v>0.6606</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0875</v>
+        <v>-0.435</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.089</v>
+        <v>0.0433</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0721</v>
+        <v>0.0793</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1612</v>
+        <v>-0.0361</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5649999999999999</v>
+        <v>-0.3698</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5649999999999999</v>
+        <v>-0.1745</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. SCHOTT</t>
+          <t>A. SOLA IDDRISU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9189000000000001</v>
+        <v>0.8123</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4812</v>
+        <v>0.654</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4001</v>
+        <v>0.1583</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3606</v>
+        <v>-0.4968</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0554</v>
+        <v>-0.0944</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6948</v>
+        <v>-0.4024</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4043</v>
+        <v>0.2404</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6721</v>
+        <v>0.9855</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2677</v>
+        <v>-0.7451</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0437</v>
+        <v>-0.7372</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3834</v>
+        <v>-1.0799</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4271</v>
+        <v>0.3426</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3219</v>
+        <v>-0.3434</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0769</v>
+        <v>-0.1514</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3988</v>
+        <v>-0.192</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V. ARTEAGA GONZALEZ</t>
+          <t>E. VICEDO AYALA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9124</v>
+        <v>0.743</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1776</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7348</v>
+        <v>-0.0187</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7343</v>
+        <v>3.0145</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0737</v>
+        <v>1.7546</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6606</v>
+        <v>1.2599</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0251</v>
+        <v>3.7406</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0251</v>
+        <v>1.8249</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.9157</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7091</v>
+        <v>-0.7261</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0486</v>
+        <v>-0.0703</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6606</v>
+        <v>-0.6558</v>
       </c>
       <c r="P17" t="n">
         <v>-0.435</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6525</v>
+        <v>1.7401</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0171</v>
+        <v>-0.5113</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4146</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4317</v>
+        <v>0.2926</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3698</v>
+        <v>-1.3252</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.1745</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1952</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7259</v>
+        <v>0.541</v>
       </c>
       <c r="E18" t="n">
         <v>-0.5469000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2728</v>
+        <v>1.0879</v>
       </c>
       <c r="G18" t="n">
         <v>-0.09569999999999999</v>
@@ -1858,13 +1858,13 @@
         <v>0.87</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.2758</v>
       </c>
       <c r="T18" t="n">
         <v>-0.4675</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3766</v>
+        <v>0.1917</v>
       </c>
       <c r="V18" t="n">
         <v>1.13</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. VICEDO AYALA</t>
+          <t>F. SCHOTT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5039</v>
+        <v>0.2818</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5381</v>
+        <v>-0.9282</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0342</v>
+        <v>1.2101</v>
       </c>
       <c r="G19" t="n">
-        <v>3.0145</v>
+        <v>-0.3606</v>
       </c>
       <c r="H19" t="n">
-        <v>1.7546</v>
+        <v>-1.0554</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2599</v>
+        <v>0.6948</v>
       </c>
       <c r="J19" t="n">
-        <v>3.7406</v>
+        <v>-0.4043</v>
       </c>
       <c r="K19" t="n">
-        <v>1.8249</v>
+        <v>-0.6721</v>
       </c>
       <c r="L19" t="n">
-        <v>1.9157</v>
+        <v>0.2677</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7261</v>
+        <v>0.0437</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0703</v>
+        <v>-0.3834</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6558</v>
+        <v>0.4271</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7504</v>
+        <v>-0.3151</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0274</v>
+        <v>-0.5239</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2771</v>
+        <v>0.2088</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.3252</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.3252</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.139</v>
+        <v>-0.0696</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5113</v>
+        <v>-1.2878</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3724</v>
+        <v>1.2183</v>
       </c>
       <c r="G20" t="n">
         <v>-1.5347</v>
@@ -2014,13 +2014,13 @@
         <v>1.305</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0907</v>
+        <v>0.1601</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.262</v>
+        <v>-0.0384</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3527</v>
+        <v>0.1986</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5046</v>
+        <v>-0.2176</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.802</v>
+        <v>-2.5785</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2974</v>
+        <v>2.3609</v>
       </c>
       <c r="G21" t="n">
         <v>0.3724</v>
@@ -2092,13 +2092,13 @@
         <v>1.9576</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.7471</v>
+        <v>-1.4601</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2209</v>
+        <v>-0.9974</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.5262</v>
+        <v>-0.4627</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1226</v>
+        <v>-2.2356</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0542</v>
+        <v>-0.3928</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1767</v>
+        <v>-1.8428</v>
       </c>
       <c r="G22" t="n">
         <v>0.8074</v>
@@ -2170,13 +2170,13 @@
         <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2997</v>
+        <v>-0.4128</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4026</v>
+        <v>-0.0445</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7023</v>
+        <v>-0.3683</v>
       </c>
       <c r="V22" t="n">
         <v>-1.3252</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4085</v>
+        <v>-3.1542</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4042</v>
+        <v>-2.1806</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0044</v>
+        <v>-0.9736</v>
       </c>
       <c r="G23" t="n">
         <v>-3.8761</v>
@@ -2248,13 +2248,13 @@
         <v>0.6525</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1849</v>
+        <v>0.0694</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2055</v>
+        <v>0.018</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0205</v>
+        <v>0.0514</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>6.509699999999999</v>
+        <v>8.745100000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0259</v>
+        <v>1.025999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>5.484</v>
+        <v>7.719200000000002</v>
       </c>
       <c r="G24" t="n">
         <v>10.6979</v>
@@ -2302,7 +2302,7 @@
         <v>12.9424</v>
       </c>
       <c r="K24" t="n">
-        <v>8.396099999999999</v>
+        <v>8.396100000000001</v>
       </c>
       <c r="L24" t="n">
         <v>4.546</v>
@@ -2317,7 +2317,7 @@
         <v>0.7688000000000003</v>
       </c>
       <c r="P24" t="n">
-        <v>3.262499999999999</v>
+        <v>3.2625</v>
       </c>
       <c r="Q24" t="n">
         <v>-11.9629</v>
@@ -2326,16 +2326,16 @@
         <v>15.2254</v>
       </c>
       <c r="S24" t="n">
-        <v>-7.450599999999999</v>
+        <v>-5.2154</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.494200000000001</v>
+        <v>-4.4943</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.9565</v>
+        <v>-0.7211</v>
       </c>
       <c r="V24" t="n">
-        <v>-9.999999999998899e-05</v>
+        <v>-0.000100000000000211</v>
       </c>
       <c r="W24" t="n">
         <v>4.5406</v>
